--- a/data/trans_dic/P64D$bicicleta_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P64D$bicicleta_2023-Clase-trans_dic.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,02</t>
+          <t>1,45; 5,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,87</t>
+          <t>0,9; 2,97</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,45</t>
+          <t>0,63; 5,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,17</t>
+          <t>0,26; 2,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,81</t>
+          <t>0,57; 2,82</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>0,0; 3,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,45</t>
+          <t>0,0; 5,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,26</t>
+          <t>0,19; 3,43</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,39</t>
+          <t>0,15; 1,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,54</t>
+          <t>0,19; 1,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,17</t>
+          <t>0,26; 1,11</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,56</t>
+          <t>0,07; 0,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 58,45</t>
+          <t>0,05; 54,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 40,95</t>
+          <t>0,11; 35,67</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -822,84 +822,33 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,73; 2,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,46; 20,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,84; 12,12</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>0,74; 1,92</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0,48; 23,14</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0,87; 11,23</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:A15"/>
@@ -914,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -927,7 +876,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5081; 17622</t>
+          <t>5092; 18081</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4299</t>
+          <t>0; 5180</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5973; 19071</t>
+          <t>5941; 19680</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1914; 13510</t>
+          <t>1907; 15343</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>662; 5482</t>
+          <t>666; 5509</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3314; 15616</t>
+          <t>3186; 15692</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 17809</t>
+          <t>0; 18156</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5455</t>
+          <t>0; 4373</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>977; 18331</t>
+          <t>1080; 19299</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1011; 7799</t>
+          <t>835; 8016</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>632; 6581</t>
+          <t>802; 6684</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2651; 11587</t>
+          <t>2562; 10900</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1273,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>153; 1347</t>
+          <t>158; 1398</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>193; 218262</t>
+          <t>192; 202038</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>566; 251143</t>
+          <t>665; 218812</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1351,17 +1300,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>77326</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101609</t>
         </is>
       </c>
     </row>
@@ -1397,109 +1346,35 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14149; 39074</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6598; 296983</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28365; 409881</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>24283</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>77326</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>101609</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>14301; 37304</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>6898; 332658</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>29252; 379682</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P64D$bicicleta_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P64D$bicicleta_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,15</t>
+          <t>1,59; 5,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,97</t>
+          <t>0,97; 2,97</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,06</t>
+          <t>0,58; 4,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,18</t>
+          <t>0,75; 4,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,82</t>
+          <t>0,87; 3,38</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,71</t>
+          <t>0,45; 5,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,97</t>
+          <t>0,0; 5,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,43</t>
+          <t>0,75; 4,7</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,43</t>
+          <t>0,36; 2,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,57</t>
+          <t>0,18; 1,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,11</t>
+          <t>0,43; 1,57</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,58</t>
+          <t>0,71; 8,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 54,1</t>
+          <t>0,23; 2,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 35,67</t>
+          <t>0,64; 4,83</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,01</t>
+          <t>1,33; 3,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,46; 20,65</t>
+          <t>0,54; 1,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 12,12</t>
+          <t>1,08; 2,13</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9993</t>
+          <t>11329</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>12788</t>
         </is>
       </c>
     </row>
@@ -981,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5092; 18081</t>
+          <t>6080; 19618</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5180</t>
+          <t>0; 5135</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5941; 19680</t>
+          <t>6934; 21198</t>
         </is>
       </c>
     </row>
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>10186</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1907; 15343</t>
+          <t>1860; 14952</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>666; 5509</t>
+          <t>2045; 11169</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3186; 15692</t>
+          <t>5157; 20096</t>
         </is>
       </c>
     </row>
@@ -1104,17 +1104,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>7093</t>
         </is>
       </c>
     </row>
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 18156</t>
+          <t>1208; 15227</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4373</t>
+          <t>0; 4253</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1080; 19299</t>
+          <t>2641; 16654</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>9728</t>
         </is>
       </c>
     </row>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>835; 8016</t>
+          <t>2262; 13713</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>802; 6684</t>
+          <t>873; 8562</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2562; 10900</t>
+          <t>4757; 17277</t>
         </is>
       </c>
     </row>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>69943</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70447</t>
+          <t>11393</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>158; 1398</t>
+          <t>2177; 27162</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>192; 202038</t>
+          <t>707; 7219</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>665; 218812</t>
+          <t>3940; 29913</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>24283</t>
+          <t>37928</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>77326</t>
+          <t>13260</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>101609</t>
+          <t>51189</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14149; 39074</t>
+          <t>25279; 58729</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6598; 296983</t>
+          <t>8015; 21344</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28365; 409881</t>
+          <t>36478; 71998</t>
         </is>
       </c>
     </row>
